--- a/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,12 +472,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AEN25H</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AEN25J</t>
+          <t>AR2011</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,19 +514,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>AEN25H</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GEN28Q</t>
+          <t>AEN25J</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GEN2BJ</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 0 mål (diff 19)</t>
+          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GEN2BK</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GEN2LD</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Svenska: 24 mål, engelska: 0 mål (diff 24)</t>
+          <t>Svenska: 31 mål, engelska: 0 mål (diff 31)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GEN37A</t>
+          <t>GEN28Q</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN2BJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
+          <t>Svenska: 19 mål, engelska: 0 mål (diff 19)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN2BK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>GEN2LD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 24 mål, engelska: 0 mål (diff 24)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GEN37A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Svenska: 18 mål, engelska: 0 mål (diff 18)</t>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Svenska: 44 mål, engelska: 0 mål (diff 44)</t>
+          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Svenska: 46 mål, engelska: 0 mål (diff 46)</t>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Svenska: 44 mål, engelska: 0 mål (diff 44)</t>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Svenska: 46 mål, engelska: 0 mål (diff 46)</t>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GPR3GM</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 11 mål (diff 1)</t>
+          <t>Svenska: 5 mål, engelska: 4 mål (diff 1)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 10 mål (diff 1)</t>
+          <t>Svenska: 37 mål, engelska: 0 mål (diff 37)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+          <t>Svenska: 32 mål, engelska: 0 mål (diff 32)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 18 mål, engelska: 0 mål (diff 18)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
+          <t>Svenska: 44 mål, engelska: 0 mål (diff 44)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Svenska: 33 mål, engelska: 0 mål (diff 33)</t>
+          <t>Svenska: 46 mål, engelska: 0 mål (diff 46)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 78 mål, engelska: 0 mål (diff 78)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Svenska: 31 mål, engelska: 0 mål (diff 31)</t>
+          <t>Svenska: 44 mål, engelska: 0 mål (diff 44)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 46 mål, engelska: 0 mål (diff 46)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1464,19 +1464,19 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GPR3GM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 12 mål, engelska: 11 mål (diff 1)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+          <t>Svenska: 11 mål, engelska: 10 mål (diff 1)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GPR3GP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>ASP25D</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>ASP25E</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSP28C</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+          <t>Svenska: 33 mål, engelska: 0 mål (diff 33)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 38 mål, engelska: 1 mål (diff 37)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+          <t>Svenska: 31 mål, engelska: 0 mål (diff 31)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 21 mål, engelska: 0 mål (diff 21)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 0 mål (diff 22)</t>
+          <t>Svenska: 32 mål, engelska: 0 mål (diff 32)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GTY2SW</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 53 mål, engelska: 0 mål (diff 53)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Svenska: 36 mål, engelska: 0 mål (diff 36)</t>
+          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Svenska: 34 mål, engelska: 0 mål (diff 34)</t>
+          <t>Svenska: 19 mål, engelska: 0 mål (diff 19)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Svenska: 37 mål, engelska: 0 mål (diff 37)</t>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+          <t>Svenska: 53 mål, engelska: 0 mål (diff 53)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>TY1038</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,44 +2026,827 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BN</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GSS3C7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GSS3H8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HB</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HG</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HJ</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GSS3K2</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>SS2007</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZU</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZV</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DD</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DF</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ATY255</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ATY256</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Svenska: 22 mål, engelska: 0 mål (diff 22)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>GTY2ST</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GTY2SW</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GTY32H</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CT</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Svenska: 36 mål, engelska: 0 mål (diff 36)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Svenska: 34 mål, engelska: 0 mål (diff 34)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J9</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Svenska: 37 mål, engelska: 0 mål (diff 37)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>TY1038</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
           <t>TY1067</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E60"/>
+  <autoFilter ref="A1:E89"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2183,6 +2966,64 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$89</definedName>

--- a/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$89</definedName>

--- a/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+          <t>Svenska: 25 mål, engelska: 1 mål (diff 24)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Svenska: 31 mål, engelska: 0 mål (diff 31)</t>
+          <t>Svenska: 20 mål, engelska: 1 mål (diff 19)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GEN28Q</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GEN2BJ</t>
+          <t>GEN28Q</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 0 mål (diff 19)</t>
+          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GEN2BK</t>
+          <t>GEN2BJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+          <t>Svenska: 19 mål, engelska: 1 mål (diff 18)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>GEN2BK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 17 mål, engelska: 1 mål (diff 16)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GEN2LD</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>GEN2LD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Svenska: 24 mål, engelska: 0 mål (diff 24)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GEN37A</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN37A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
+          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+          <t>Svenska: 26 mål, engelska: 1 mål (diff 25)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 4 mål (diff 1)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Svenska: 37 mål, engelska: 0 mål (diff 37)</t>
+          <t>Svenska: 5 mål, engelska: 4 mål (diff 1)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Svenska: 32 mål, engelska: 0 mål (diff 32)</t>
+          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Svenska: 18 mål, engelska: 0 mål (diff 18)</t>
+          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Svenska: 44 mål, engelska: 0 mål (diff 44)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Svenska: 46 mål, engelska: 0 mål (diff 46)</t>
+          <t>Svenska: 18 mål, engelska: 1 mål (diff 17)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Svenska: 78 mål, engelska: 0 mål (diff 78)</t>
+          <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Svenska: 44 mål, engelska: 0 mål (diff 44)</t>
+          <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Svenska: 46 mål, engelska: 0 mål (diff 46)</t>
+          <t>Svenska: 78 mål, engelska: 1 mål (diff 77)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
+          <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
+          <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GPR3GM</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 11 mål (diff 1)</t>
+          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 10 mål (diff 1)</t>
+          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+          <t>Svenska: 20 mål, engelska: 1 mål (diff 19)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>GPR3GM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 12 mål, engelska: 11 mål (diff 1)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 11 mål, engelska: 10 mål (diff 1)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>GPR3GP</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Svenska: 33 mål, engelska: 0 mål (diff 33)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GRY36F</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Svenska: 38 mål, engelska: 1 mål (diff 37)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Svenska: 31 mål, engelska: 0 mål (diff 31)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>ASP25D</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 0 mål (diff 21)</t>
+          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>ASP25E</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
+          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSP28C</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Svenska: 32 mål, engelska: 0 mål (diff 32)</t>
+          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Svenska: 53 mål, engelska: 0 mål (diff 53)</t>
+          <t>Svenska: 33 mål, engelska: 1 mål (diff 32)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 0 mål (diff 19)</t>
+          <t>Svenska: 38 mål, engelska: 1 mål (diff 37)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GSP2W6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Svenska: 53 mål, engelska: 0 mål (diff 53)</t>
+          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>ASS26C</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSS2BY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS2BZ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS2C4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSS2C5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>GSS2C6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2274,14 +2274,14 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSS2FJ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+          <t>Svenska: 21 mål, engelska: 2 mål (diff 19)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 0 mål (diff 25)</t>
+          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 0 mål (diff 20)</t>
+          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 0 mål (diff 23)</t>
+          <t>Svenska: 19 mål, engelska: 2 mål (diff 17)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 0 mål (diff 22)</t>
+          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GSS36C</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GTY2SW</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GSS39Q</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Svenska: 36 mål, engelska: 0 mål (diff 36)</t>
+          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Svenska: 34 mål, engelska: 0 mål (diff 34)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Svenska: 37 mål, engelska: 0 mål (diff 37)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>TY1038</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GSS3BM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,44 +2809,1799 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>GSS3BN</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BP</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>GSS3C6</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>GSS3C7</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>GSS3H8</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>GSS3H9</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HB</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HC</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HD</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HD</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HE</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HF</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HG</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 2 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HH</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HJ</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>SS2007</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>SS3002</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>SS3003</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>SS3004</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>SS3006</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>SS3007</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>SS3008</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>SS3009</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>SS3010</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>SS3011</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>SS3014</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>ASV29Z</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>ASV2A2</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>GSV2BN</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>GSV2BP</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>GSV2P9</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZU</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZV</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DD</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DF</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>GSV3JE</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>ATY255</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>ATY256</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Svenska: 22 mål, engelska: 1 mål (diff 21)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GTY2ST</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>GTY2SW</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>GTY32H</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CT</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Svenska: 36 mål, engelska: 1 mål (diff 35)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Svenska: 34 mål, engelska: 1 mål (diff 33)</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J9</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>TY1038</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>TY1049</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>TY1050</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
           <t>TY1067</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>TY1068</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>TY1070</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>TY1071</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>TY2004</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>TY3012</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>TY3013</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E89"/>
+  <autoFilter ref="A1:E154"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3024,6 +4779,136 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$228</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AR2011</t>
+          <t>AR2010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,29 +509,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AEN25H</t>
+          <t>AR2011</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -541,46 +541,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AEN25J</t>
+          <t>AR2011</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>AEN25H</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 1 mål (diff 24)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>AEN25H</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -617,24 +617,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>AEN25J</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>AEN25J</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 1 mål (diff 19)</t>
+          <t>Svenska: 25 mål, engelska: 1 mål (diff 24)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -725,24 +725,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GEN28Q</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GEN2BJ</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 1 mål (diff 18)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GEN2BK</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Svenska: 17 mål, engelska: 1 mål (diff 16)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GEN2JG</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -833,24 +833,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GEN2LD</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
+          <t>Svenska: 20 mål, engelska: 1 mål (diff 19)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GEN2QW</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
+          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GEN37A</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN28Q</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Svenska: 26 mål, engelska: 1 mål (diff 25)</t>
+          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN2BJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
+          <t>Svenska: 19 mål, engelska: 1 mål (diff 18)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN2BJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GEN2BK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,51 +1054,51 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
+          <t>Svenska: 17 mål, engelska: 1 mål (diff 16)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>GEN2BK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,51 +1108,51 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>GEN2JG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 4 mål (diff 1)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GEN2LD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1162,51 +1162,51 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
+          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GEN2LD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,51 +1216,51 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GEN2QW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,51 +1270,51 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Svenska: 18 mål, engelska: 1 mål (diff 17)</t>
+          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GEN37A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,51 +1324,51 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
+          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GEN37A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Svenska: 78 mål, engelska: 1 mål (diff 77)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,51 +1378,51 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
+          <t>Svenska: 26 mål, engelska: 1 mål (diff 25)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,51 +1486,51 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
+          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,51 +1540,51 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 1 mål (diff 19)</t>
+          <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GPR3GM</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 11 mål (diff 1)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,51 +1594,51 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 10 mål (diff 1)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,51 +1648,51 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GRY36F</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 4 mål (diff 1)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1729,51 +1729,51 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,51 +1810,51 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
+          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,51 +1864,51 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Svenska: 33 mål, engelska: 1 mål (diff 32)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,51 +1918,51 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Svenska: 38 mål, engelska: 1 mål (diff 37)</t>
+          <t>Svenska: 18 mål, engelska: 1 mål (diff 17)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GSP2W6</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,51 +1972,51 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
+          <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,51 +2026,51 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ASS26C</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,51 +2080,51 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 78 mål, engelska: 1 mål (diff 77)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GSS22M</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GSS22P</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,51 +2134,51 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GSS2BY</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GSS2BZ</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,51 +2188,51 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GSS2C4</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GSS2C5</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GSS2C6</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GSS2FJ</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,51 +2350,51 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 2 mål (diff 19)</t>
+          <t>Svenska: 20 mål, engelska: 1 mål (diff 19)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GPR3GM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
+          <t>Svenska: 12 mål, engelska: 11 mål (diff 1)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
+          <t>Svenska: 11 mål, engelska: 10 mål (diff 1)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GPR3GP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 2 mål (diff 17)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GRY36F</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSS36C</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSS39P</t>
+          <t>ASP25D</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,51 +2620,51 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSS39Q</t>
+          <t>ASP25D</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>ASP25E</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,51 +2674,51 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
+          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>ASP25E</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GSP28C</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,51 +2755,51 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 33 mål, engelska: 1 mål (diff 32)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSS3BM</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,51 +2809,51 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSS3BP</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 38 mål, engelska: 1 mål (diff 37)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GSP2W6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,46 +2917,46 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
+          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GSS3H9</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,19 +2971,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GSS3HC</t>
+          <t>ASS26C</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSS3HD</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3057,14 +3057,14 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSS3HE</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSS3HF</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS2BY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 2 mål (diff 14)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSS3HH</t>
+          <t>GSS2BZ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3160,19 +3160,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS2C4</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS2C5</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>GSS2C6</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSS2FJ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SS3002</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3295,19 +3295,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SS3003</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3317,24 +3317,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 21 mål, engelska: 2 mål (diff 19)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SS3006</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3371,24 +3371,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>SS3008</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3430,19 +3430,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3452,24 +3452,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>SS3010</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3484,19 +3484,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SS3014</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3538,24 +3538,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3565,51 +3565,51 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 19 mål, engelska: 2 mål (diff 17)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ASV2A2</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3619,51 +3619,51 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GSV2BN</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3673,51 +3673,51 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSV2BP</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSV2P9</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>GSS36C</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSS39Q</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3835,51 +3835,51 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
+          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3889,24 +3889,24 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3943,24 +3943,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3970,51 +3970,51 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>GSS3BM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4051,51 +4051,51 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 1 mål (diff 21)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GTY2SW</t>
+          <t>GSS3BP</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4132,24 +4132,24 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4159,51 +4159,51 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Svenska: 36 mål, engelska: 1 mål (diff 35)</t>
+          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Svenska: 34 mål, engelska: 1 mål (diff 33)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4213,51 +4213,51 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TY1038</t>
+          <t>GSS3H9</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4294,51 +4294,51 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GSS3HC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>TY1067</t>
+          <t>GSS3HD</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HD</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>TY1068</t>
+          <t>GSS3HE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,24 +4402,24 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>TY1070</t>
+          <t>GSS3HF</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4429,24 +4429,24 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4456,51 +4456,51 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 16 mål, engelska: 2 mål (diff 14)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>TY2004</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>GSS3HH</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,71 +4537,2069 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>GSS3K2</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (4 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>SS2007</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>SS2007</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>SS3002</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>SS3003</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>SS3004</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>SS3006</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>SS3007</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>SS3008</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>SS3009</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>SS3010</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>SS3011</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>SS3014</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>ASV29Z</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>ASV2A2</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CP</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>ASV2CQ</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>GSV2BN</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>GSV2BP</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>GSV2P9</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZU</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZU</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZV</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZV</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DD</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DD</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DF</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DF</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>GSV3FP</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>GSV3JE</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>ATY255</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>ATY255</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>ATY256</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>ATY256</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Svenska: 22 mål, engelska: 1 mål (diff 21)</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>GTY2ST</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>GTY2ST</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>GTY2SW</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>GTY2SW</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>GTY32H</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>GTY32H</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CT</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Svenska: 36 mål, engelska: 1 mål (diff 35)</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CT</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Svenska: 34 mål, engelska: 1 mål (diff 33)</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J9</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J9</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>TY1038</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>TY1038</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>TY1049</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>TY1050</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>TY1067</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>TY1067</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>TY1068</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>TY1070</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>TY1071</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>TY2004</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>TY3012</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
           <t>TY3013</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
         <is>
           <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E154"/>
+  <autoFilter ref="A1:E228"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4909,6 +6907,154 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$G$228</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E228"/>
+  <dimension ref="A1:G228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2015-09-15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
@@ -509,15 +531,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2010</t>
         </is>
@@ -536,15 +568,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
@@ -563,15 +605,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2017-10-03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2011</t>
         </is>
@@ -590,15 +642,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
@@ -617,15 +675,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
@@ -644,15 +708,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
@@ -671,15 +741,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
@@ -698,15 +774,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2015-03-16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Svenska: 25 mål, engelska: 1 mål (diff 24)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
@@ -725,15 +807,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>2015-03-16</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
@@ -752,15 +840,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
@@ -779,15 +873,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
@@ -806,15 +906,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
@@ -833,15 +939,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
@@ -860,15 +972,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Svenska: 20 mål, engelska: 1 mål (diff 19)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
@@ -887,15 +1005,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
@@ -914,15 +1038,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2018-03-22</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
@@ -941,15 +1071,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>2018-03-22</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
@@ -968,15 +1104,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2019-03-21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
         </is>
@@ -995,15 +1141,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Svenska: 19 mål, engelska: 1 mål (diff 18)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
         </is>
@@ -1022,15 +1174,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
         </is>
@@ -1049,15 +1207,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Svenska: 17 mål, engelska: 1 mål (diff 16)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
         </is>
@@ -1076,15 +1240,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
         </is>
@@ -1103,15 +1273,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
@@ -1130,15 +1306,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
@@ -1157,15 +1339,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2020-12-23</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
         </is>
@@ -1184,15 +1372,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>2020-12-23</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
         </is>
@@ -1211,15 +1405,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
@@ -1238,15 +1438,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
@@ -1265,15 +1471,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
@@ -1292,15 +1504,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
@@ -1319,15 +1537,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
         </is>
@@ -1346,15 +1570,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
         </is>
@@ -1373,15 +1603,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Svenska: 26 mål, engelska: 1 mål (diff 25)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
@@ -1400,15 +1636,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
@@ -1427,15 +1669,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
@@ -1454,15 +1702,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
@@ -1481,15 +1735,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
@@ -1508,15 +1768,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
@@ -1535,15 +1801,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Svenska: 14 mål, engelska: 1 mål (diff 13)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
@@ -1562,15 +1834,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
@@ -1589,15 +1867,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
@@ -1616,15 +1900,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
@@ -1643,15 +1933,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
@@ -1670,15 +1966,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
@@ -1697,15 +1999,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 4 mål (diff 1)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
@@ -1724,15 +2032,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
@@ -1751,15 +2065,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
@@ -1778,15 +2098,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
@@ -1805,15 +2131,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
@@ -1832,15 +2164,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
@@ -1859,15 +2197,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2022-11-29</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
@@ -1886,15 +2230,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>2022-11-29</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
@@ -1913,15 +2263,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Svenska: 18 mål, engelska: 1 mål (diff 17)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
@@ -1940,15 +2296,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
@@ -1967,15 +2329,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
@@ -1994,15 +2362,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
@@ -2021,15 +2395,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
@@ -2048,15 +2428,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
@@ -2075,15 +2461,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Svenska: 78 mål, engelska: 1 mål (diff 77)</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
@@ -2102,15 +2494,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
@@ -2129,15 +2527,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
@@ -2156,15 +2560,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
@@ -2183,15 +2593,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
@@ -2210,15 +2626,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
@@ -2237,15 +2659,25 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
@@ -2264,15 +2696,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
@@ -2291,15 +2729,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
@@ -2318,15 +2762,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
@@ -2345,15 +2795,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Svenska: 20 mål, engelska: 1 mål (diff 19)</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
@@ -2372,15 +2828,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
@@ -2399,15 +2861,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Svenska: 12 mål, engelska: 11 mål (diff 1)</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
         </is>
@@ -2426,15 +2894,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Svenska: 11 mål, engelska: 10 mål (diff 1)</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
@@ -2453,15 +2927,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
@@ -2480,15 +2960,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
@@ -2507,15 +2993,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
@@ -2534,15 +3026,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
         </is>
@@ -2561,15 +3059,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
@@ -2588,15 +3092,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
@@ -2615,15 +3125,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
@@ -2642,15 +3158,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
@@ -2669,15 +3191,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
@@ -2696,15 +3224,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
@@ -2723,15 +3257,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>2019-03-13</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
@@ -2750,15 +3290,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>Svenska: 33 mål, engelska: 1 mål (diff 32)</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
@@ -2777,15 +3327,25 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
@@ -2804,15 +3364,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
@@ -2831,15 +3397,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
@@ -2858,15 +3430,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Svenska: 38 mål, engelska: 1 mål (diff 37)</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
@@ -2885,15 +3463,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
         </is>
@@ -2912,15 +3496,25 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
@@ -2939,15 +3533,25 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
@@ -2966,15 +3570,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
@@ -2993,15 +3603,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
@@ -3020,15 +3636,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
@@ -3047,15 +3669,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
@@ -3074,15 +3702,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
@@ -3101,15 +3735,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+          <t>2018-04-19</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
@@ -3128,15 +3768,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+          <t>2019-11-18</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
         </is>
@@ -3155,15 +3801,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
+          <t>2019-11-18</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
         </is>
@@ -3182,15 +3834,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
+          <t>2019-11-18</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
         </is>
@@ -3209,15 +3867,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+          <t>2019-11-18</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
         </is>
@@ -3236,15 +3900,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
+          <t>2019-11-18</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
         </is>
@@ -3263,15 +3933,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+          <t>2020-03-10</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
         </is>
@@ -3290,15 +3966,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
+          <t>2020-03-10</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
@@ -3317,15 +3999,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
+          <t>2020-03-10</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
@@ -3344,15 +4032,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Svenska: 21 mål, engelska: 2 mål (diff 19)</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
@@ -3371,15 +4065,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
@@ -3398,15 +4098,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+          <t>2020-04-27</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
@@ -3425,15 +4131,21 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
@@ -3452,15 +4164,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
@@ -3479,15 +4197,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
@@ -3506,15 +4230,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
@@ -3533,15 +4263,21 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
@@ -3560,15 +4296,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Svenska: 19 mål, engelska: 2 mål (diff 17)</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
@@ -3587,15 +4329,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
@@ -3614,15 +4362,21 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
@@ -3641,15 +4395,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
@@ -3668,15 +4428,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
@@ -3695,15 +4461,21 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
@@ -3722,15 +4494,21 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
@@ -3749,15 +4527,21 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
         </is>
@@ -3776,15 +4560,21 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
@@ -3803,15 +4593,21 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
         </is>
@@ -3830,15 +4626,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
@@ -3857,15 +4659,21 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
@@ -3884,15 +4692,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
@@ -3911,15 +4725,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
@@ -3938,15 +4758,21 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
@@ -3965,15 +4791,21 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
@@ -3992,15 +4824,21 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
@@ -4019,15 +4857,21 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
         </is>
@@ -4046,15 +4890,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
@@ -4073,15 +4923,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
@@ -4100,15 +4956,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
         </is>
@@ -4127,15 +4989,21 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
@@ -4154,15 +5022,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
@@ -4181,15 +5055,21 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
@@ -4208,15 +5088,21 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
@@ -4235,15 +5121,21 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
@@ -4262,15 +5154,21 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
         </is>
@@ -4289,15 +5187,21 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
@@ -4316,15 +5220,21 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
@@ -4343,15 +5253,21 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
         </is>
@@ -4370,15 +5286,21 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HD</t>
         </is>
@@ -4397,15 +5319,21 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
@@ -4424,15 +5352,21 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
@@ -4451,15 +5385,21 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>Svenska: 16 mål, engelska: 2 mål (diff 14)</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
@@ -4478,15 +5418,21 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
@@ -4505,15 +5451,21 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
         </is>
@@ -4532,15 +5484,21 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
         <is>
           <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
@@ -4559,15 +5517,21 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
@@ -4586,15 +5550,21 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (4 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
@@ -4613,15 +5583,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
         <is>
           <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
@@ -4640,15 +5616,25 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
           <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
@@ -4667,15 +5653,25 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
@@ -4694,15 +5690,21 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
         <is>
           <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -4721,15 +5723,21 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -4748,15 +5756,21 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
+          <t>2014-03-20</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
         </is>
@@ -4775,15 +5789,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
+          <t>2014-03-20</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
         </is>
@@ -4802,15 +5822,21 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
+          <t>2014-04-11</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
@@ -4829,15 +5855,21 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
         <is>
           <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
         </is>
@@ -4856,15 +5888,21 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
@@ -4883,15 +5921,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
         </is>
@@ -4910,15 +5954,21 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
@@ -4937,15 +5987,21 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
+          <t>2015-12-14</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
@@ -4964,15 +6020,21 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
+          <t>2016-06-09</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
         <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
@@ -4991,15 +6053,21 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
+          <t>2016-11-18</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
@@ -5018,15 +6086,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
         <is>
           <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
@@ -5045,15 +6119,21 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
         <is>
           <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
@@ -5072,15 +6152,21 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
@@ -5099,15 +6185,21 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
@@ -5126,15 +6218,21 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
@@ -5153,15 +6251,21 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
         <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
@@ -5180,15 +6284,21 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
         <is>
           <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
         </is>
@@ -5207,15 +6317,21 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
         <is>
           <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
@@ -5234,15 +6350,21 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
@@ -5261,15 +6383,21 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
         <is>
           <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
@@ -5288,15 +6416,21 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
@@ -5315,15 +6449,21 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
         <is>
           <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
@@ -5342,15 +6482,21 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
@@ -5369,15 +6515,21 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
         <is>
           <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
@@ -5396,15 +6548,21 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
@@ -5423,15 +6581,21 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
         <is>
           <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
@@ -5450,15 +6614,21 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
@@ -5477,15 +6647,21 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
         <is>
           <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
@@ -5504,15 +6680,21 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
@@ -5531,15 +6713,21 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
         <is>
           <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
@@ -5558,15 +6746,21 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
@@ -5585,15 +6779,21 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
@@ -5612,15 +6812,21 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
@@ -5639,15 +6845,21 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
         <is>
           <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
@@ -5666,15 +6878,21 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
@@ -5693,15 +6911,21 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
         <is>
           <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
@@ -5720,15 +6944,21 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="F196" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
@@ -5747,15 +6977,21 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
         <is>
           <t>Svenska: 22 mål, engelska: 1 mål (diff 21)</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
@@ -5774,15 +7010,21 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
@@ -5801,15 +7043,21 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
         <is>
           <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
@@ -5828,15 +7076,21 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
@@ -5855,15 +7109,21 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
         <is>
           <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
         </is>
@@ -5882,15 +7142,21 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="F202" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
         </is>
@@ -5909,15 +7175,21 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
         <is>
           <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
@@ -5936,15 +7208,21 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
@@ -5963,15 +7241,21 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
         <is>
           <t>Svenska: 36 mål, engelska: 1 mål (diff 35)</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
@@ -5990,15 +7274,21 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="F206" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
@@ -6017,15 +7307,21 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
         <is>
           <t>Svenska: 34 mål, engelska: 1 mål (diff 33)</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
@@ -6044,15 +7340,21 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
@@ -6071,15 +7373,21 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
         <is>
           <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
@@ -6098,15 +7406,21 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
@@ -6125,15 +7439,21 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
         <is>
           <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
@@ -6152,15 +7472,21 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
@@ -6179,15 +7505,25 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2011-10-10</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
           <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
         </is>
@@ -6206,15 +7542,25 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
+          <t>2011-10-10</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
         </is>
@@ -6233,15 +7579,25 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
           <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
@@ -6260,15 +7616,25 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
@@ -6287,15 +7653,25 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
           <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
@@ -6314,15 +7690,25 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
@@ -6341,15 +7727,25 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2015-03-06</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
           <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
         </is>
@@ -6368,15 +7764,25 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
+          <t>2015-03-06</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
         </is>
@@ -6395,15 +7801,21 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
         </is>
@@ -6422,15 +7834,21 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
         <is>
           <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
         </is>
@@ -6449,15 +7867,21 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
         <is>
           <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
         </is>
@@ -6476,15 +7900,25 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2008-05-29</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
           <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
         </is>
@@ -6503,15 +7937,25 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
@@ -6530,15 +7974,25 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
           <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
@@ -6557,15 +8011,25 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
           <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
@@ -6584,477 +8048,487 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
           <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E228"/>
+  <autoFilter ref="A1:G228"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId304"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId312"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId316"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId322"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId330"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId336"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId338"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId342"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId344"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId346"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId352"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId354"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId356"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId362"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId364"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId366"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId368"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId374"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId376"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId378"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId382"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId386"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId388"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId390"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId392"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId394"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId396"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId400"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId404"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId406"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId408"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId410"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId412"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId414"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId416"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId418"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId420"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId422"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId424"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId426"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId428"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId430"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId432"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId434"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId436"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId438"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId440"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId442"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId444"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId446"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId450"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId452"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId454"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$G$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$G$229</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G228"/>
+  <dimension ref="A1:G229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1857,17 +1857,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>GEN3KC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 22 mål, engelska: 1 mål (diff 21)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3KC</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1939,17 +1939,17 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
@@ -1972,12 +1972,12 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -1989,7 +1989,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GFR2R3</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1999,30 +1999,30 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 4 mål (diff 1)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2R3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
+          <t>Svenska: 5 mål, engelska: 4 mål (diff 1)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R3</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2098,30 +2098,30 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
@@ -2170,12 +2170,12 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2263,23 +2263,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svenska: 18 mål, engelska: 1 mål (diff 17)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2302,12 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 18 mål, engelska: 1 mål (diff 17)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2329,23 +2329,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2368,12 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2401,17 +2401,17 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2461,23 +2461,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svenska: 78 mål, engelska: 1 mål (diff 77)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
@@ -2500,12 +2500,12 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 78 mål, engelska: 1 mål (diff 77)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2527,23 +2527,23 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
@@ -2566,12 +2566,12 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 44 mål, engelska: 1 mål (diff 43)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -2583,7 +2583,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2599,17 +2599,17 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2632,12 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 46 mål, engelska: 1 mål (diff 45)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -2649,57 +2649,57 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>GIT2T6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2020-03-12</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -2707,19 +2707,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2740,19 +2740,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
+          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2773,19 +2773,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
+          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2806,12 +2806,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 1 mål (diff 19)</t>
+          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 20 mål, engelska: 1 mål (diff 19)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -2851,40 +2851,40 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GPR3GM</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 11 mål (diff 1)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GPR3GM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2905,19 +2905,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 10 mål (diff 1)</t>
+          <t>Svenska: 12 mål, engelska: 11 mål (diff 1)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2938,29 +2938,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+          <t>Svenska: 11 mål, engelska: 10 mål (diff 1)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GRY2HL</t>
+          <t>GPR3GP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2971,19 +2971,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GRY2HL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3009,14 +3009,14 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2HL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GRY36F</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3037,19 +3037,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GRY36G</t>
+          <t>GRY36F</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3075,14 +3075,14 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36F</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GRY36H</t>
+          <t>GRY36G</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3108,24 +3108,24 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>GRY36H</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY36H</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3164,12 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>ASP25D</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3197,17 +3197,17 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>ASP25E</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3257,30 +3257,30 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2019-03-13</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GSP28C</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3290,14 +3290,10 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
+          <t>2019-03-13</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -3305,12 +3301,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svenska: 33 mål, engelska: 1 mål (diff 32)</t>
+          <t>Svenska: 12 mål, engelska: 1 mål (diff 11)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3333,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 33 mål, engelska: 1 mål (diff 32)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3354,7 +3350,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3364,23 +3360,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
@@ -3403,12 +3403,12 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3430,30 +3430,30 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svenska: 38 mål, engelska: 1 mål (diff 37)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSP2W6</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -3474,19 +3474,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 38 mål, engelska: 1 mål (diff 37)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GSP2W6</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3499,11 +3499,7 @@
           <t>2022-04-28</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2023-11-02</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -3511,12 +3507,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3539,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 31 mål, engelska: 1 mål (diff 30)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3560,40 +3556,44 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3619,14 +3619,14 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ASS26C</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3647,19 +3647,19 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>ASS26C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3680,19 +3680,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSS22M</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3713,19 +3713,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSS22P</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3746,19 +3746,19 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSS2BY</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2019-11-18</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3779,19 +3779,19 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSS2BZ</t>
+          <t>GSS2BY</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3812,19 +3812,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSS2C4</t>
+          <t>GSS2BZ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3845,19 +3845,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GSS2C5</t>
+          <t>GSS2C4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3883,14 +3883,14 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GSS2C6</t>
+          <t>GSS2C5</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3911,19 +3911,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSS2FJ</t>
+          <t>GSS2C6</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2019-11-18</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -3949,14 +3949,14 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>GSS2FJ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
         </is>
       </c>
     </row>
@@ -4005,12 +4005,12 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4032,23 +4032,23 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-10</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 2 mål (diff 19)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 21 mål, engelska: 2 mål (diff 19)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4098,30 +4098,30 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
+          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4170,12 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4197,23 +4197,23 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
@@ -4236,12 +4236,12 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4263,30 +4263,30 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -4307,12 +4307,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 2 mål (diff 17)</t>
+          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 19 mål, engelska: 2 mål (diff 17)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4362,23 +4362,23 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4401,12 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4428,23 +4428,23 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4494,30 +4494,30 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSS36C</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4538,19 +4538,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSS39P</t>
+          <t>GSS36C</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -4576,14 +4576,14 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSS39Q</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4609,14 +4609,14 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS39Q</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4665,12 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4698,24 +4698,24 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4741,14 +4741,14 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4774,14 +4774,14 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -4802,12 +4802,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
@@ -4830,12 +4830,12 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GSS3BM</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4863,24 +4863,24 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSS3BM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -4946,7 +4946,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GSS3BP</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4962,24 +4962,24 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GSS3BP</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -5000,19 +5000,19 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -5078,7 +5078,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5088,23 +5088,23 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
@@ -5127,12 +5127,12 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSS3H9</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5160,24 +5160,24 @@
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSS3H9</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
         </is>
       </c>
     </row>
@@ -5226,12 +5226,12 @@
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -5243,7 +5243,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSS3HC</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5259,24 +5259,24 @@
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSS3HD</t>
+          <t>GSS3HC</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5302,14 +5302,14 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSS3HE</t>
+          <t>GSS3HD</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5335,14 +5335,14 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HD</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSS3HF</t>
+          <t>GSS3HE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5368,14 +5368,14 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS3HF</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 2 mål (diff 14)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 16 mål, engelska: 2 mål (diff 14)</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GSS3HH</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5457,24 +5457,24 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS3HH</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -5561,19 +5561,19 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (4 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5583,30 +5583,30 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
+          <t>Learning Outcomes skrivet som löpande text (4 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5616,14 +5616,10 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2016-11-17</t>
-        </is>
-      </c>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -5631,12 +5627,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
@@ -5663,12 +5659,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -5680,7 +5676,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5693,20 +5689,24 @@
           <t>2013-02-04</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SS3002</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5756,30 +5756,30 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2014-03-20</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>SS3003</t>
+          <t>SS3002</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5800,19 +5800,19 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>SS3003</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2014-04-11</t>
+          <t>2014-03-20</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -5838,14 +5838,14 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SS3006</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2014-04-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -5866,19 +5866,19 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>SS3006</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5899,19 +5899,19 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>SS3008</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5937,14 +5937,14 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>SS3008</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5965,19 +5965,19 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>SS3010</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2015-12-14</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -5998,19 +5998,19 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>SS3010</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2016-06-09</t>
+          <t>2015-12-14</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -6031,19 +6031,19 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>SS3014</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2016-11-18</t>
+          <t>2016-06-09</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -6064,29 +6064,29 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>SS3014</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2016-11-18</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -6097,19 +6097,19 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ASV2A2</t>
+          <t>ASV29Z</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6135,14 +6135,14 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>ASV2A2</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -6163,19 +6163,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6201,14 +6201,14 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GSV2BN</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -6229,19 +6229,19 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GSV2BP</t>
+          <t>GSV2BN</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6262,19 +6262,19 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GSV2P9</t>
+          <t>GSV2BP</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -6295,19 +6295,19 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>GSV2P9</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -6328,12 +6328,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
         </is>
       </c>
     </row>
@@ -6356,12 +6356,12 @@
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6389,17 +6389,17 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6455,17 +6455,17 @@
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
@@ -6488,12 +6488,12 @@
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -6505,7 +6505,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6521,17 +6521,17 @@
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6581,23 +6581,23 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
@@ -6620,12 +6620,12 @@
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6653,17 +6653,17 @@
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
@@ -6686,12 +6686,12 @@
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6719,17 +6719,17 @@
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
@@ -6752,12 +6752,12 @@
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6779,30 +6779,30 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -6828,24 +6828,24 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -6856,12 +6856,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -6901,7 +6901,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>ATY255</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6917,17 +6917,17 @@
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
       </c>
     </row>
@@ -6950,12 +6950,12 @@
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>ATY256</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6977,23 +6977,23 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 1 mål (diff 21)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
       </c>
     </row>
@@ -7016,12 +7016,12 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 22 mål, engelska: 1 mål (diff 21)</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7043,23 +7043,23 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
@@ -7082,12 +7082,12 @@
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GTY2SW</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7115,17 +7115,17 @@
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
@@ -7148,12 +7148,12 @@
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY2SW</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7175,23 +7175,23 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7241,23 +7241,23 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Svenska: 36 mål, engelska: 1 mål (diff 35)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
@@ -7280,12 +7280,12 @@
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 36 mål, engelska: 1 mål (diff 35)</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -7297,7 +7297,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7313,17 +7313,17 @@
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Svenska: 34 mål, engelska: 1 mål (diff 33)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
@@ -7346,12 +7346,12 @@
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 34 mål, engelska: 1 mål (diff 33)</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -7363,7 +7363,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7373,23 +7373,23 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
@@ -7412,12 +7412,12 @@
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7445,17 +7445,17 @@
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
@@ -7478,12 +7478,12 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -7495,7 +7495,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>TY1038</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7505,27 +7505,23 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2011-10-10</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
@@ -7552,12 +7548,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -7569,7 +7565,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>TY1038</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7579,34 +7575,34 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2011-10-10</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2013-08-01</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>TY1049</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7621,7 +7617,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2013-08-01</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7631,19 +7627,19 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>TY1050</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7653,7 +7649,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -7668,12 +7664,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
       </c>
     </row>
@@ -7700,12 +7696,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -7717,7 +7713,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>TY1067</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7727,27 +7723,27 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2015-03-06</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
@@ -7774,12 +7770,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -7791,7 +7787,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>TY1068</t>
+          <t>TY1067</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7801,30 +7797,34 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>2015-03-06</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2023-01-27</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>TY1070</t>
+          <t>TY1068</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -7845,19 +7845,19 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>TY1070</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7878,19 +7878,19 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>TY2004</t>
+          <t>TY1071</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7900,14 +7900,10 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2008-05-29</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>2013-08-01</t>
-        </is>
-      </c>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -7915,19 +7911,19 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY2004</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7937,12 +7933,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2008-05-29</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2013-08-01</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -7952,19 +7948,19 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7989,19 +7985,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8011,7 +8007,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -8026,54 +8022,91 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
+          <t>TY3012</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
           <t>TY3013</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="C229" t="inlineStr">
         <is>
           <t>2013-11-07</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
         <is>
           <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G228"/>
+  <autoFilter ref="A1:G229"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -8529,6 +8562,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId452"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId456"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Samstämmighet svenska och engelska.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$G$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$G$235</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G229"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3593,17 +3593,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3614,52 +3614,52 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 34 mål, engelska: 1 mål (diff 33)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ASS26C</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3680,19 +3680,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3718,14 +3718,14 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSS22M</t>
+          <t>ASS26C</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -3746,19 +3746,19 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS26C</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSS22P</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3779,19 +3779,19 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSS2BY</t>
+          <t>GSS22M</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2019-11-18</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -3812,19 +3812,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22M</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSS2BZ</t>
+          <t>GSS22P</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2019-11-18</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3845,19 +3845,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS22P</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GSS2C4</t>
+          <t>GSS2BY</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3878,19 +3878,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BY</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GSS2C5</t>
+          <t>GSS2BZ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3911,19 +3911,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2BZ</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSS2C6</t>
+          <t>GSS2C4</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3944,19 +3944,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSS2FJ</t>
+          <t>GSS2C5</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2019-11-18</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -3977,19 +3977,19 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>GSS2C6</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2019-11-18</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -4010,19 +4010,19 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2C6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>GSS2FJ</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4038,24 +4038,24 @@
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FJ</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-10</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -4076,19 +4076,19 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 2 mål (diff 19)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-10</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -4114,14 +4114,14 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -4142,19 +4142,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
+          <t>Svenska: 21 mål, engelska: 2 mål (diff 19)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4164,30 +4164,30 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4197,30 +4197,30 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -4241,19 +4241,19 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
+          <t>Svenska: 32 mål, engelska: 1 mål (diff 31)</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -4274,19 +4274,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -4307,19 +4307,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
+          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4329,30 +4329,30 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 2 mål (diff 17)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4362,30 +4362,30 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 24 mål, engelska: 1 mål (diff 23)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -4406,19 +4406,19 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
+          <t>Svenska: 19 mål, engelska: 2 mål (diff 17)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -4444,14 +4444,14 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -4472,19 +4472,19 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
+          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -4510,14 +4510,14 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4538,19 +4538,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
+          <t>Svenska: 53 mål, engelska: 2 mål (diff 51)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSS36C</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4560,30 +4560,30 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSS39P</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -4604,19 +4604,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 21 mål, engelska: 1 mål (diff 20)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSS39Q</t>
+          <t>GSS36C</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4642,14 +4642,14 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS36C</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4662,7 +4662,11 @@
           <t>2023-12-19</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -4670,19 +4674,19 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS39Q</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4695,27 +4699,31 @@
           <t>2023-12-19</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSS39S</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4728,7 +4736,11 @@
           <t>2023-12-19</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -4736,19 +4748,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GSS39T</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4761,27 +4773,31 @@
           <t>2023-12-19</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GSS39U</t>
+          <t>GSS39S</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4807,14 +4823,14 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39S</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS39T</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4824,7 +4840,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -4835,19 +4851,19 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39T</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS39U</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4857,30 +4873,30 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39U</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GSS3BM</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4901,19 +4917,19 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4929,24 +4945,24 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSS3BM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4962,24 +4978,24 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BM</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSS3BP</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5000,19 +5016,19 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5022,30 +5038,30 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSS3BP</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5055,7 +5071,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -5066,19 +5082,19 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BP</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSS3C6</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5094,24 +5110,24 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5121,10 +5137,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -5132,19 +5152,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5154,10 +5174,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>Saknar punktlista (en)</t>
@@ -5170,14 +5194,14 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GSS3H9</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5198,19 +5222,19 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5220,30 +5244,30 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSS3H9</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5253,30 +5277,30 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSS3HC</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5297,19 +5321,19 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSS3HD</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5325,24 +5349,24 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSS3HE</t>
+          <t>GSS3HC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5368,14 +5392,14 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSS3HF</t>
+          <t>GSS3HD</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5401,14 +5425,14 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HD</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS3HE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5429,19 +5453,19 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 2 mål (diff 14)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS3HF</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5457,24 +5481,24 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HF</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GSS3HH</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5495,19 +5519,19 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 16 mål, engelska: 2 mål (diff 14)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5523,24 +5547,24 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS3HH</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5556,24 +5580,24 @@
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HH</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5583,30 +5607,30 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (4 mål utan punktlista)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5616,30 +5640,30 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5649,34 +5673,30 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2016-11-17</t>
-        </is>
-      </c>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Learning Outcomes skrivet som löpande text (4 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5686,34 +5706,30 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2016-11-17</t>
-        </is>
-      </c>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 26 mål, engelska: 0 mål (diff 26)</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5726,7 +5742,11 @@
           <t>2013-02-04</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -5734,19 +5754,19 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5759,7 +5779,11 @@
           <t>2013-02-04</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>Saknar punktlista (en)</t>
@@ -5772,14 +5796,14 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>SS3002</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5789,10 +5813,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2014-03-20</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -5800,19 +5828,19 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 23 mål, engelska: 1 mål (diff 22)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>SS3003</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5822,30 +5850,34 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2014-03-20</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SS3004</t>
+          <t>SS3002</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5855,7 +5887,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2014-04-11</t>
+          <t>2014-03-20</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -5866,19 +5898,19 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3002</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>SS3006</t>
+          <t>SS3003</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5888,7 +5920,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2014-03-20</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -5899,19 +5931,19 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3003</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>SS3007</t>
+          <t>SS3004</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5921,7 +5953,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2014-04-11</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -5932,19 +5964,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3004</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>SS3008</t>
+          <t>SS3006</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5965,19 +5997,19 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3006</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>SS3009</t>
+          <t>SS3007</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5998,19 +6030,19 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3007</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>SS3010</t>
+          <t>SS3008</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6020,7 +6052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2015-12-14</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -6031,19 +6063,19 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3008</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>SS3009</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6053,7 +6085,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2016-06-09</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -6069,14 +6101,14 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3009</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>SS3014</t>
+          <t>SS3010</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6086,7 +6118,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2016-11-18</t>
+          <t>2015-12-14</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -6097,29 +6129,29 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3010</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2016-06-09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -6130,29 +6162,29 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ASV2A2</t>
+          <t>SS3014</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2016-11-18</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -6163,19 +6195,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3014</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>ASV29Z</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6185,7 +6217,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -6196,19 +6228,19 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>ASV2A2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6218,7 +6250,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -6229,19 +6261,19 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GSV2BN</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6251,7 +6283,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -6262,19 +6294,19 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GSV2BP</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6284,7 +6316,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -6295,19 +6327,19 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GSV2P9</t>
+          <t>BSV22A</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6317,7 +6349,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -6328,19 +6360,19 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BSV22A</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>GSV2BN</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6350,7 +6382,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -6361,19 +6393,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BN</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>GSV2BP</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6383,30 +6415,30 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2BP</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSV2P9</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6416,7 +6448,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -6427,19 +6459,19 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6455,24 +6487,24 @@
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6488,24 +6520,24 @@
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6521,24 +6553,24 @@
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6554,24 +6586,24 @@
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6587,24 +6619,24 @@
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6614,30 +6646,30 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6647,30 +6679,30 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 25 mål, engelska: 2 mål (diff 23)</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6680,30 +6712,30 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6719,24 +6751,24 @@
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 20 mål, engelska: 2 mål (diff 18)</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6752,24 +6784,24 @@
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6785,24 +6817,24 @@
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6812,30 +6844,30 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6845,7 +6877,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -6856,95 +6888,95 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 23 mål, engelska: 2 mål (diff 21)</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -6955,52 +6987,52 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>GSV3KH</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3KH</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>ATY255</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7010,7 +7042,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -7021,19 +7053,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 1 mål (diff 21)</t>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>ATY255</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7043,7 +7075,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -7059,14 +7091,14 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>ATY256</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7076,7 +7108,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -7087,19 +7119,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>ATY256</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7109,7 +7141,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -7125,14 +7157,14 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GTY2SW</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7142,7 +7174,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -7153,19 +7185,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Svenska: 22 mål, engelska: 1 mål (diff 21)</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GTY2SW</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7175,7 +7207,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -7191,14 +7223,14 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7208,7 +7240,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -7219,19 +7251,19 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7241,7 +7273,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -7257,14 +7289,14 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY2SW</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7274,7 +7306,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -7285,19 +7317,19 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Svenska: 36 mål, engelska: 1 mål (diff 35)</t>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY2SW</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7307,7 +7339,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -7323,14 +7355,14 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7340,7 +7372,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -7351,19 +7383,19 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Svenska: 34 mål, engelska: 1 mål (diff 33)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7373,7 +7405,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -7389,14 +7421,14 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7406,7 +7438,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -7417,19 +7449,19 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
+          <t>Svenska: 36 mål, engelska: 1 mål (diff 35)</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7439,7 +7471,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -7455,14 +7487,14 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7472,7 +7504,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -7483,19 +7515,19 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+          <t>Svenska: 34 mål, engelska: 1 mål (diff 33)</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7505,7 +7537,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -7521,14 +7553,14 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>TY1038</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7538,14 +7570,10 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2011-10-10</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -7553,19 +7581,19 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Svenska: 37 mål, engelska: 1 mål (diff 36)</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>TY1038</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7575,14 +7603,10 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2011-10-10</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>Saknar punktlista (en)</t>
@@ -7595,14 +7619,14 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7612,14 +7636,10 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2013-08-01</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -7627,19 +7647,19 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7649,34 +7669,30 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3KG</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7686,14 +7702,10 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -7701,19 +7713,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 38 mål, engelska: 1 mål (diff 37)</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3KG</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7723,14 +7735,10 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>Saknar punktlista (en)</t>
@@ -7743,14 +7751,14 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>TY1067</t>
+          <t>TY1038</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7760,12 +7768,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2015-03-06</t>
+          <t>2011-10-10</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -7775,19 +7783,19 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>TY1067</t>
+          <t>TY1038</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7797,12 +7805,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2015-03-06</t>
+          <t>2011-10-10</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7817,14 +7825,14 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>TY1068</t>
+          <t>TY1049</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7834,10 +7842,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -7845,19 +7857,19 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>TY1070</t>
+          <t>TY1050</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7867,10 +7879,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -7878,19 +7894,19 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7900,10 +7916,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -7911,19 +7931,19 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>TY2004</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7933,34 +7953,34 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2008-05-29</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2013-08-01</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1067</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7970,12 +7990,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2015-03-06</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -7985,19 +8005,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY1067</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8007,34 +8027,34 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2015-03-06</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1067</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>TY1068</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -8044,14 +8064,10 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2015-10-05</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -8059,54 +8075,268 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1068</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
+          <t>TY1070</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>TY1071</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>TY2004</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2008-05-29</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>TY3012</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
           <t>TY3013</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>2013-11-07</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
         <is>
           <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G229"/>
+  <autoFilter ref="A1:G235"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -8564,6 +8794,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId454"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId468"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
